--- a/Attendance_2026_10_25.xlsx
+++ b/Attendance_2026_10_25.xlsx
@@ -16,11 +16,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;ل.س.‏&quot;_-;\-* #,##0.00\ &quot;ل.س.‏&quot;_-;_-* &quot;-&quot;??\ &quot;ل.س.‏&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="166" formatCode="hh:mm"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="hh:mm"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00\ &quot;ل.س.‏&quot;_-;\-* #,##0.00\ &quot;ل.س.‏&quot;_-;_-* &quot;-&quot;??\ &quot;ل.س.‏&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -111,6 +111,11 @@
       <color rgb="FFFF0000"/>
       <sz val="16"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -190,9 +195,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -242,14 +247,23 @@
     <xf numFmtId="20" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -681,13 +695,13 @@
           <t>Omar Elnemr</t>
         </is>
       </c>
-      <c r="C2" s="17" t="n">
+      <c r="C2" s="20" t="n">
         <v>46320</v>
       </c>
-      <c r="D2" s="18" t="n">
+      <c r="D2" s="21" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="E2" s="18" t="n">
+      <c r="E2" s="21" t="n">
         <v>0.1319444444444444</v>
       </c>
       <c r="F2" s="7" t="n"/>
@@ -717,13 +731,13 @@
           <t>Mohammad Almohammad</t>
         </is>
       </c>
-      <c r="C3" s="17" t="n">
+      <c r="C3" s="20" t="n">
         <v>46320</v>
       </c>
-      <c r="D3" s="18" t="n">
+      <c r="D3" s="21" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="E3" s="18" t="n">
+      <c r="E3" s="21" t="n">
         <v>0.8055555555555556</v>
       </c>
       <c r="F3" s="8" t="n"/>
@@ -753,13 +767,13 @@
           <t>Hanan Tinawi</t>
         </is>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="20" t="n">
         <v>46320</v>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="21" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="21" t="n">
         <v>0.125</v>
       </c>
       <c r="F4" s="8" t="n"/>
@@ -789,14 +803,18 @@
           <t>Osama Alkabbani</t>
         </is>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="20" t="n">
         <v>46320</v>
       </c>
-      <c r="D5" s="16" t="n">
-        <v>0.3541666666666667</v>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>0.6875</v>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
       </c>
       <c r="F5" s="8" t="n"/>
       <c r="G5" s="8" t="n"/>
@@ -825,14 +843,18 @@
           <t>Yasmin Tatary</t>
         </is>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="20" t="n">
         <v>46320</v>
       </c>
-      <c r="D6" s="16" t="n">
-        <v>0.3541666666666667</v>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>0.6875</v>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
       </c>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -861,14 +883,18 @@
           <t>Joudi Alghorani</t>
         </is>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="20" t="n">
         <v>46320</v>
       </c>
-      <c r="D7" s="16" t="n">
-        <v>0.3541666666666667</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>0.6875</v>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
       </c>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
@@ -897,13 +923,13 @@
           <t>Khaled Mohammad Mlas</t>
         </is>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="20" t="n">
         <v>46320</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="21" t="n">
         <v>0.8298611111111112</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="21" t="n">
         <v>0.09722222222222222</v>
       </c>
       <c r="F8" s="8" t="n"/>
@@ -933,14 +959,18 @@
           <t>Raboushee</t>
         </is>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="20" t="n">
         <v>46320</v>
       </c>
-      <c r="D9" s="16" t="n">
-        <v>0.3541666666666667</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>0.6875</v>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
       </c>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
@@ -969,13 +999,13 @@
           <t>Rasheed Akel</t>
         </is>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="20" t="n">
         <v>46320</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="21" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="21" t="n">
         <v>0.8055555555555556</v>
       </c>
       <c r="F10" s="8" t="n"/>

--- a/Attendance_2026_10_25.xlsx
+++ b/Attendance_2026_10_25.xlsx
@@ -197,7 +197,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -264,6 +264,12 @@
     </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -629,9 +635,9 @@
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="10.7109375" bestFit="1" customWidth="1" style="9" min="4" max="5"/>
     <col width="9.140625" customWidth="1" style="9" min="6" max="7"/>
-    <col width="29" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" style="10" min="9" max="9"/>
-    <col width="20.5703125" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" style="10" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -686,7 +692,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="21" customHeight="1">
+    <row r="2" ht="24" customHeight="1">
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
@@ -711,7 +717,7 @@
           <t>عمر النمر</t>
         </is>
       </c>
-      <c r="I2" s="13" t="inlineStr">
+      <c r="I2" s="23" t="inlineStr">
         <is>
           <t>Night Shift (out next day 03:10 AM)</t>
         </is>
@@ -722,7 +728,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="21" customHeight="1">
+    <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
@@ -747,7 +753,7 @@
           <t>محمد المحمد</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="23" t="inlineStr">
         <is>
           <t>Extended Shift</t>
         </is>
@@ -758,7 +764,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="21" customHeight="1">
+    <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
@@ -783,7 +789,7 @@
           <t>حنان تيناوي</t>
         </is>
       </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="I4" s="23" t="inlineStr">
         <is>
           <t>Night Shift (out next day 03:00 AM)</t>
         </is>
@@ -794,7 +800,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="21" customHeight="1">
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
@@ -823,9 +829,9 @@
           <t>اسامة القباني</t>
         </is>
       </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>OFF (Paid off day)</t>
+      <c r="I5" s="23" t="inlineStr">
+        <is>
+          <t>OFF (Rest Day)</t>
         </is>
       </c>
       <c r="J5" s="12" t="inlineStr">
@@ -834,7 +840,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="21" customHeight="1">
+    <row r="6" ht="24" customHeight="1">
       <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
@@ -863,9 +869,9 @@
           <t>ياسمين ططري</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>OFF</t>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>OFF (Rest Day)</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
@@ -874,7 +880,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="21" customHeight="1">
+    <row r="7" ht="24" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
@@ -903,9 +909,9 @@
           <t>جودي الغوراني</t>
         </is>
       </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>OFF</t>
+      <c r="I7" s="23" t="inlineStr">
+        <is>
+          <t>OFF (Rest Day)</t>
         </is>
       </c>
       <c r="J7" s="12" t="inlineStr">
@@ -914,7 +920,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="21" customHeight="1">
+    <row r="8" ht="24" customHeight="1">
       <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
@@ -939,7 +945,7 @@
           <t>محمد خالد ملص</t>
         </is>
       </c>
-      <c r="I8" s="13" t="inlineStr">
+      <c r="I8" s="23" t="inlineStr">
         <is>
           <t>Night Shift (out next day 02:20 AM)</t>
         </is>
@@ -950,7 +956,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="21" customHeight="1">
+    <row r="9" ht="24" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
@@ -979,9 +985,9 @@
           <t xml:space="preserve">ربى </t>
         </is>
       </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>OFF</t>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>OFF (Rest Day)</t>
         </is>
       </c>
       <c r="J9" s="12" t="inlineStr">
@@ -990,7 +996,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="18.75" customHeight="1">
+    <row r="10" ht="24" customHeight="1">
       <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
@@ -1015,7 +1021,7 @@
           <t>رشيد عاقل</t>
         </is>
       </c>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="I10" s="24" t="inlineStr">
         <is>
           <t>Extended Shift</t>
         </is>
